--- a/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/03_Hızlı Müdahale ve Problem Çözme/EKG-KLT-FRM-02_8d_duzeltici_ve_onleyici_faaliyet_formu__dolu_ornek.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/03_Hızlı Müdahale ve Problem Çözme/EKG-KLT-FRM-02_8d_duzeltici_ve_onleyici_faaliyet_formu__dolu_ornek.xlsx
@@ -2277,7 +2277,8 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="0" differentOddEven="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-02&amp;C&amp;"Arial,Regular"&amp;11 8D Düzeltici ve Önleyici Faaliyet Formu - Dolu Örnek</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 28.09.2026
+Revizyon nedeni: Dolu 8D formu 2018 kaynak örneği olarak işaretlendi; işlem ve tarih bilgileri korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2305,7 +2306,8 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="0" differentOddEven="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-02&amp;C&amp;"Arial,Regular"&amp;11 8D Düzeltici ve Önleyici Faaliyet Formu - Dolu Örnek</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 28.09.2026
+Revizyon nedeni: Dolu 8D formu 2018 kaynak örneği olarak işaretlendi; işlem ve tarih bilgileri korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
